--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.74645883681086</v>
+        <v>6.296299560981764</v>
       </c>
       <c r="D2" t="n">
-        <v>38.78512497150169</v>
+        <v>6.302582807869026</v>
       </c>
       <c r="E2" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F2" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.730745821208099</v>
+        <v>0.9312461959463162</v>
       </c>
       <c r="D3" t="n">
-        <v>5.646093927952871</v>
+        <v>0.9174902632923416</v>
       </c>
       <c r="E3" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F3" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.89164965080356</v>
+        <v>5.182393068255579</v>
       </c>
       <c r="D4" t="n">
-        <v>31.78250493761569</v>
+        <v>5.16465705236255</v>
       </c>
       <c r="E4" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F4" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.08540636851592</v>
+        <v>3.263878534883838</v>
       </c>
       <c r="D5" t="n">
-        <v>19.93807374463051</v>
+        <v>3.239936983502458</v>
       </c>
       <c r="E5" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F5" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>80.12886551831478</v>
+        <v>13.02094064672615</v>
       </c>
       <c r="D6" t="n">
-        <v>80.15613834539577</v>
+        <v>13.02537248112681</v>
       </c>
       <c r="E6" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F6" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.6731368793593</v>
+        <v>5.309384742895886</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33435455925621</v>
+        <v>5.254332615879135</v>
       </c>
       <c r="E7" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F7" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.52940535147587</v>
+        <v>5.61102836961483</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96123784621533</v>
+        <v>5.51870115000999</v>
       </c>
       <c r="E8" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F8" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.49633976345245</v>
+        <v>8.205655211561023</v>
       </c>
       <c r="D9" t="n">
-        <v>50.51893035362106</v>
+        <v>8.209326182463423</v>
       </c>
       <c r="E9" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F9" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.012999884560033</v>
+        <v>0.4896124812410054</v>
       </c>
       <c r="D10" t="n">
-        <v>2.365282507570682</v>
+        <v>0.3843584074802358</v>
       </c>
       <c r="E10" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F10" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.82827644569833</v>
+        <v>7.122094922425979</v>
       </c>
       <c r="D11" t="n">
-        <v>41.43923815882324</v>
+        <v>6.733876200808776</v>
       </c>
       <c r="E11" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F11" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.93686461727159</v>
+        <v>1.777240500306634</v>
       </c>
       <c r="D12" t="n">
-        <v>10.9712648907546</v>
+        <v>1.782830544747622</v>
       </c>
       <c r="E12" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F12" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.876864391834271</v>
+        <v>1.604990463673069</v>
       </c>
       <c r="D13" t="n">
-        <v>10.01230906612037</v>
+        <v>1.62700022324456</v>
       </c>
       <c r="E13" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F13" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.677238774617313</v>
+        <v>1.410051300875313</v>
       </c>
       <c r="D14" t="n">
-        <v>8.565138188274787</v>
+        <v>1.391834955594653</v>
       </c>
       <c r="E14" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F14" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.61112353693377</v>
+        <v>6.274307574751737</v>
       </c>
       <c r="D15" t="n">
-        <v>38.74421746939485</v>
+        <v>6.295935338776663</v>
       </c>
       <c r="E15" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F15" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.90790559502283</v>
+        <v>5.022534659191209</v>
       </c>
       <c r="D16" t="n">
-        <v>30.18973287842317</v>
+        <v>4.905831592743765</v>
       </c>
       <c r="E16" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F16" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.58528252631072</v>
+        <v>4.320108410525492</v>
       </c>
       <c r="D17" t="n">
-        <v>26.73105432451992</v>
+        <v>4.343796327734488</v>
       </c>
       <c r="E17" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F17" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.7231879470104</v>
+        <v>5.31751804138919</v>
       </c>
       <c r="D18" t="n">
-        <v>18.4398421299581</v>
+        <v>2.996474346118192</v>
       </c>
       <c r="E18" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F18" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.62985297540076</v>
+        <v>6.764851108502624</v>
       </c>
       <c r="D19" t="n">
-        <v>9.261629326299868</v>
+        <v>1.505014765523729</v>
       </c>
       <c r="E19" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F19" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>62.24672362215534</v>
+        <v>10.11509258860024</v>
       </c>
       <c r="D20" t="n">
-        <v>35.38374019651941</v>
+        <v>5.749857781934405</v>
       </c>
       <c r="E20" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F20" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>36.52388176574887</v>
+        <v>5.935130786934192</v>
       </c>
       <c r="D21" t="n">
-        <v>17.66371197468611</v>
+        <v>2.870353195886493</v>
       </c>
       <c r="E21" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F21" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>32.1914315061675</v>
+        <v>5.231107619752218</v>
       </c>
       <c r="D22" t="n">
-        <v>32.24977921563879</v>
+        <v>5.240589122541303</v>
       </c>
       <c r="E22" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F22" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>48.13432344953238</v>
+        <v>7.821827560549012</v>
       </c>
       <c r="D23" t="n">
-        <v>19.06742406028727</v>
+        <v>3.098456409796682</v>
       </c>
       <c r="E23" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F23" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>11.42577603011505</v>
+        <v>1.856688604893696</v>
       </c>
       <c r="D24" t="n">
-        <v>12.16389906957819</v>
+        <v>1.976633598806456</v>
       </c>
       <c r="E24" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F24" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>60.5061602210961</v>
+        <v>9.832251035928115</v>
       </c>
       <c r="D25" t="n">
-        <v>10.23324912992457</v>
+        <v>1.662902983612743</v>
       </c>
       <c r="E25" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F25" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>39.22517464373059</v>
+        <v>6.374090879606221</v>
       </c>
       <c r="D26" t="n">
-        <v>26.628781017126</v>
+        <v>4.327176915282975</v>
       </c>
       <c r="E26" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F26" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>58.84228966472534</v>
+        <v>9.561872070517868</v>
       </c>
       <c r="D27" t="n">
-        <v>19.97242997693755</v>
+        <v>3.245519871252351</v>
       </c>
       <c r="E27" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F27" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>57.84940923107025</v>
+        <v>9.400529000048916</v>
       </c>
       <c r="D28" t="n">
-        <v>38.01640653103447</v>
+        <v>6.177666061293102</v>
       </c>
       <c r="E28" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F28" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>11.48060072192428</v>
+        <v>1.865597617312696</v>
       </c>
       <c r="D29" t="n">
-        <v>11.23721333845159</v>
+        <v>1.826047167498383</v>
       </c>
       <c r="E29" t="n">
-        <v>19.19553164034574</v>
+        <v>3.119273891556183</v>
       </c>
       <c r="F29" t="n">
-        <v>16.32359526135903</v>
+        <v>2.652584229970843</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
